--- a/artfynd/A 26933-2024 artfynd.xlsx
+++ b/artfynd/A 26933-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86572649</v>
+        <v>135477173</v>
       </c>
       <c r="B3" t="n">
-        <v>5179</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,42 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tavelån O Smalmyran, Anumark, Vb</t>
+          <t>Anumark, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>765082</v>
+        <v>765007</v>
       </c>
       <c r="R3" t="n">
-        <v>7090198</v>
+        <v>7090051</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,28 +868,23 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86572651</v>
+        <v>86572649</v>
       </c>
       <c r="B4" t="n">
         <v>5179</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>765093</v>
+        <v>765082</v>
       </c>
       <c r="R4" t="n">
-        <v>7090178</v>
+        <v>7090198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86572652</v>
+        <v>86572651</v>
       </c>
       <c r="B5" t="n">
         <v>5179</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765092</v>
+        <v>765093</v>
       </c>
       <c r="R5" t="n">
-        <v>7090174</v>
+        <v>7090178</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86572648</v>
+        <v>86572652</v>
       </c>
       <c r="B6" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765087</v>
+        <v>765092</v>
       </c>
       <c r="R6" t="n">
-        <v>7090201</v>
+        <v>7090174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,6 +1202,113 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86572648</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tavelån O Smalmyran, Anumark, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>765087</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7090201</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26933-2024 artfynd.xlsx
+++ b/artfynd/A 26933-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86572654</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477173</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86572649</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86572651</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86572652</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,8 +1339,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86572648</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26933-2024 artfynd.xlsx
+++ b/artfynd/A 26933-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135477173</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26933-2024 artfynd.xlsx
+++ b/artfynd/A 26933-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86572649</v>
+        <v>135477173</v>
       </c>
       <c r="B3" t="n">
-        <v>5179</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tavelån O Smalmyran, Anumark, Vb</t>
+          <t>Anumark, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>765082</v>
+        <v>765007</v>
       </c>
       <c r="R3" t="n">
-        <v>7090198</v>
+        <v>7090051</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,33 +878,28 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86572649</t>
+          <t>https://artportalen.se/Sighting/135477173</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86572651</v>
+        <v>86572649</v>
       </c>
       <c r="B4" t="n">
         <v>5179</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>765093</v>
+        <v>765082</v>
       </c>
       <c r="R4" t="n">
-        <v>7090178</v>
+        <v>7090198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,13 +1005,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86572651</t>
+          <t>https://artportalen.se/Sighting/86572649</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86572652</v>
+        <v>86572651</v>
       </c>
       <c r="B5" t="n">
         <v>5179</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765092</v>
+        <v>765093</v>
       </c>
       <c r="R5" t="n">
-        <v>7090174</v>
+        <v>7090178</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,16 +1117,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86572652</t>
+          <t>https://artportalen.se/Sighting/86572651</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86572648</v>
+        <v>86572652</v>
       </c>
       <c r="B6" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765087</v>
+        <v>765092</v>
       </c>
       <c r="R6" t="n">
-        <v>7090201</v>
+        <v>7090174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,6 +1228,118 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86572652</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86572648</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tavelån O Smalmyran, Anumark, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>765087</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7090201</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/86572648</t>
         </is>
@@ -1240,6 +1352,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26933-2024 artfynd.xlsx
+++ b/artfynd/A 26933-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135477173</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
